--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/COROA - 29_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/COROA - 29_01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,7 +449,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>COROA FC TRILHA YES125 2004 A 2016</t>
+          <t>COROA FIXACAO CUBO  TRILHA YES125 2004 A 2016</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -474,7 +474,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>COROA FC SMARTFOX YBR125 2000 A 2008/ CRYPTON105</t>
+          <t>COROA FIXACAO CUBO  SMARTFOX YBR125 2000 A 2008/ CRYPTON105</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -499,7 +499,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>COROA FC IRON SHINERAY XY50 118970</t>
+          <t>COROA FIXACAO CUBO  IRON SHINERAY XY50 118970</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -512,6 +512,19 @@
           <t>68</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/COROA - 29_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/COROA - 29_01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,24 +492,34 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
